--- a/Exp3_PTO_GRPO/eda/results/L0/tables/1_outcomes/1_outcomes.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L0/tables/1_outcomes/1_outcomes.xlsx
@@ -434,32 +434,32 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Working Alliance</t>
+          <t>WAI-SR (Working Alliance)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Client Satisfaction</t>
+          <t>CSQ-8 (Client Satisfaction)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>MI Satisfaction</t>
+          <t>MI-SAT (MI Satisfaction)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>MI Integrity</t>
+          <t>MITI (MI Integrity)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Patient Change-Talk</t>
+          <t>PCT (Patient Change-Talk)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>MI-Inconsistency ↓</t>
+          <t>MICI (MI-Inconsistency) ↓</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">

--- a/Exp3_PTO_GRPO/eda/results/L0/tables/1_outcomes/1_outcomes.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L0/tables/1_outcomes/1_outcomes.xlsx
@@ -497,7 +497,7 @@
         <v>2.945</v>
       </c>
       <c r="F2" t="n">
-        <v>3.536</v>
+        <v>3.653</v>
       </c>
       <c r="G2" t="n">
         <v>4.273</v>
@@ -537,7 +537,7 @@
         <v>2.749</v>
       </c>
       <c r="F3" t="n">
-        <v>3.326</v>
+        <v>3.441</v>
       </c>
       <c r="G3" t="n">
         <v>4.234</v>

--- a/Exp3_PTO_GRPO/eda/results/L0/tables/1_outcomes/1_outcomes.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/L0/tables/1_outcomes/1_outcomes.xlsx
@@ -464,17 +464,17 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Reflection:Question</t>
+          <t>Reflection:Question (MITI)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>% Complex Reflections</t>
+          <t>% Complex Reflections (MITI)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>% MI-Consistent</t>
+          <t>% MI-Consistent (MITI)</t>
         </is>
       </c>
     </row>
